--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:49:33+00:00</t>
+    <t>2026-06-18T12:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitionerrole|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -394,7 +394,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -505,7 +505,7 @@
     <t>as-dr-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-practitionerrole|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-practitionerrole|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>PractitionerRole.meta.security</t>
@@ -695,7 +695,7 @@
     <t>as-ext-practitionerrole-contracted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-contracted|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -711,7 +711,7 @@
     <t>as-ext-practitionerrole-hascas</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-hascas|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -727,7 +727,7 @@
     <t>as-ext-practitionerrole-vitale-accepted</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-vitale-accepted|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1161,7 +1161,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-practitioner|1.2.0-snapshot-2)
 </t>
   </si>
   <si>
@@ -1177,7 +1177,7 @@
     <t>PractitionerRole.organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>
@@ -1413,7 +1413,7 @@
     <t>mailbox-mss</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-1}
+    <t xml:space="preserve">ContactPoint {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-mailbox-mss|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1516,7 +1516,7 @@
     <t>as-mailbox-mss-metadata</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-mailbox-mss-metadata|1.2.0-snapshot-2}
 </t>
   </si>
   <si>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:07:50+00:00</t>
+    <t>2026-06-18T13:08:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitionerrole.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-practitionerrole.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:08:38+00:00</t>
+    <t>2026-06-18T13:31:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
